--- a/10_sources_evidence.xlsx
+++ b/10_sources_evidence.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R880d8e83acab46a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="R527e613810ac4739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R8ebcfefe551247c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Re80f78c2bf5146ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="2" r:id="Rf10aef9e4d06453c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Feeds" sheetId="3" r:id="R6ab768ad7c664d99"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10313,6 +10313,66 @@
         <x:v>News / specialist maritime media</x:v>
       </x:c>
     </x:row>
+    <x:row r="503">
+      <x:c r="A503" t="str">
+        <x:v>SRC260910_025</x:v>
+      </x:c>
+      <x:c r="B503" t="str">
+        <x:v>Gulf News</x:v>
+      </x:c>
+      <x:c r="C503" t="str">
+        <x:v>Iran rocked by explosions as Trump says US-Iran war won't end until after midterm elections</x:v>
+      </x:c>
+      <x:c r="D503" t="str">
+        <x:v>https://gulfnews.com/world/mena/iran-rocked-by-explosions-as-trump-says-us-iran-war-wont-end-until-after-midterm-elections-1.500669266</x:v>
+      </x:c>
+      <x:c r="E503" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F503" t="str">
+        <x:v>Regional news / security reporting</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504">
+      <x:c r="A504" t="str">
+        <x:v>SRC260910_026</x:v>
+      </x:c>
+      <x:c r="B504" t="str">
+        <x:v>OC Media</x:v>
+      </x:c>
+      <x:c r="C504" t="str">
+        <x:v>Two Azerbaijani citizens killed in drone attack on cargo ship in Black Sea / Sea of Azov</x:v>
+      </x:c>
+      <x:c r="D504" t="str">
+        <x:v>https://oc-media.org/two-azerbaijani-citizens-killed-in-drone-attack-on-cargo-ship-in-black-sea/</x:v>
+      </x:c>
+      <x:c r="E504" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F504" t="str">
+        <x:v>Regional news / maritime security</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505">
+      <x:c r="A505" t="str">
+        <x:v>SRC260910_027</x:v>
+      </x:c>
+      <x:c r="B505" t="str">
+        <x:v>OilPrice.com</x:v>
+      </x:c>
+      <x:c r="C505" t="str">
+        <x:v>Ukraine Targets Russia's Key Black Sea Oil Port</x:v>
+      </x:c>
+      <x:c r="D505" t="str">
+        <x:v>https://oilprice.com/Latest-Energy-News/World-News/Ukraine-Targets-Russias-Key-Black-Sea-Oil-Port.html</x:v>
+      </x:c>
+      <x:c r="E505" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="F505" t="str">
+        <x:v>Energy / maritime security reporting</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
